--- a/vse-loti/340038752/spec-340038752.xlsx
+++ b/vse-loti/340038752/spec-340038752.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -35,11 +36,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,16 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,18 +458,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="15.28515625" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20.28515625" customWidth="1" min="7" max="7"/>
-    <col width="18.85546875" customWidth="1" min="8" max="8"/>
-    <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -519,35 +520,157 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Труба 20.30.95-HDPE (Бугурусланское ДУ)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>пог. м</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="4" t="n">
+        <v>1915301.23</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Бандаж B-20.25-HDPE (Бугурусланское ДУ)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="4" t="n">
+        <v>100805.33</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Труба 15.30.95-HDPE (Абдулинское ДУ)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>пог. м</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="4" t="n">
+        <v>2212188.69</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Бандаж B-15.30-HDPE (Абдулинское ДУ)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="4" t="n">
+        <v>116430.98</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n">
+      <c r="G6" s="4" t="n">
+        <v>4344726.229508197</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>НМЦК (с НДС 22%):</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>5300566</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Источник: Извещение с РТС.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>НМЦК (без НДС):</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>4344726.229508197</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>⚠ ВНИМАНИЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Труба водопропускная круглая из гофрированного металла с покрытием HDPE (т.п. 3.501.3-187.10) — металлополимерная конструкция, НЕ стальная бесшовная/электросварная труба. По ОКПД2 24.20.13.190 (формально подходит, по факту — композитный материал). Решение «ПОДХОДИТ / НЕ ПОДХОДИТ» — за Хозяином.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Источник: Дк. поставка трубы водо-ой, 5 300 566,00.doc; Извещение с РТС.docx; Часть II Проект договора на поставку трубы гофрированной, 5 300 566,00.docx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:B7"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>